--- a/SampleTemplate/Shikshalokam/Shikshalokam Project & Tasks upload Template.xlsx
+++ b/SampleTemplate/Shikshalokam/Shikshalokam Project & Tasks upload Template.xlsx
@@ -32,9 +32,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="160">
   <si>
-    <t>Template Version : 1.2.0</t>
+    <t>Template Version : 1.0.0</t>
   </si>
   <si>
     <t>General Instruction to fill this project and task upload template</t>
@@ -421,37 +421,40 @@
 NOTE: If the Learning resrources are beyond five, user can add as separate columns</t>
   </si>
   <si>
+    <t>entityType</t>
+  </si>
+  <si>
     <t>learningResources3-name</t>
   </si>
   <si>
     <t>learningResources3-link</t>
   </si>
   <si>
-    <t>Strengthening Science Concept Delivery through Structured Lesson</t>
+    <t>Test costom entity project 7</t>
   </si>
   <si>
-    <t>BHPBLMIP251</t>
+    <t>hsgdllpddaaooeehhhcc</t>
   </si>
   <si>
-    <t>shikshakparvbihar2022@gmail.com</t>
+    <t>sakshi@tan-ninety.com</t>
   </si>
   <si>
-    <t>infrastructure, community</t>
+    <t>teachers</t>
   </si>
   <si>
-    <t>Teachers will teach science and math using Project Based Learning lesson plans</t>
+    <t>To construct a wired car using a DPDT switch.</t>
   </si>
   <si>
-    <t>2 Weeks</t>
+    <t>1 year</t>
   </si>
   <si>
-    <t>PBL, MIP, Program Video, Lesson Plan, Science concept, Project-Based Learning</t>
+    <t>district</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=F_7ZoAQ3aJM&amp;pp=ygUGbmF0dXJl</t>
+    <t>Science, Activity Based Learning, STEM Education, STEM Lab, DPDT Switch Car</t>
   </si>
   <si>
-    <t>Yes</t>
+    <t>yes</t>
   </si>
   <si>
     <t>List down the taskst/sub tasks that the stakeholders has to do in order to complete the Improvement project.
@@ -464,13 +467,19 @@
 If No, the user can delete this task(delete option will show in the app for the particular task)</t>
   </si>
   <si>
-    <t>Please provide mitra bot link</t>
+    <t>isAnExternalTask</t>
+  </si>
+  <si>
+    <t>solutionType</t>
   </si>
   <si>
     <t>The name of the learning resource that you want the user to see while doing this particular task( If multiple learning resources are required. It should follow the same convention and have new column as : learningResources3-name, etc.)</t>
   </si>
   <si>
     <t>If the task has an observation, the creator defines the number of submissions required to complete a task. For example, "Number of submissions for observation" is 2 then the task is marked as complete when 2 submissions are completed.</t>
+  </si>
+  <si>
+    <t>Please provide mitra bot link</t>
   </si>
   <si>
     <t xml:space="preserve">This field is required for certificate generation.
@@ -486,6 +495,15 @@
 Note: The field is required for cerificate.</t>
   </si>
   <si>
+    <t>Solution Name</t>
+  </si>
+  <si>
+    <t>learningResources4-name</t>
+  </si>
+  <si>
+    <t>learningResources4-link</t>
+  </si>
+  <si>
     <t>Mitra_Link</t>
   </si>
   <si>
@@ -495,37 +513,70 @@
     <t>Minimum No. of Evidence for task level evidence criteria</t>
   </si>
   <si>
-    <t>BHPBLMIP1-Task1</t>
+    <t>DPDTSC-HandBook-1-2025-Task1</t>
   </si>
   <si>
-    <t>1. Teachers should understand the project based learning program</t>
+    <t>Review the Activity Manual</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>observation</t>
+  </si>
+  <si>
+    <t>test_costome_entity 7</t>
+  </si>
+  <si>
+    <t>01-08-2025</t>
+  </si>
+  <si>
+    <t>31-12-2030</t>
+  </si>
+  <si>
+    <t>DPDTSC-HandBook-1-2025-Task2</t>
+  </si>
+  <si>
+    <t>Watch the Activity Video</t>
+  </si>
+  <si>
+    <t>Activity Steps (Video)</t>
+  </si>
+  <si>
+    <t>https://youtu.be/MNvM_H9zD3Y?si=BdfslSzCkmDCggih</t>
   </si>
   <si>
     <t>No</t>
   </si>
   <si>
-    <t>BHPBLMIP1-Task2</t>
+    <t>DPDTSC-HandBook-1-2025-Task3</t>
   </si>
   <si>
-    <t>2. Teachers should implement the PBL Science lesson plan for Class 6, World of Science and upload photos or videos of the presentation</t>
+    <t>Conduct the Activity with students</t>
   </si>
   <si>
-    <t>BHPBLMIP1-Task3</t>
+    <t>DPDTSC-HandBook-1-2025-Task4</t>
   </si>
   <si>
-    <t>3. Teachers should implement the lesson plan of PBL Science for class 7, 'Who will become a nutrition expert' and upload photos or videos of the presentation</t>
+    <t xml:space="preserve">Conduct the Activity Assessment </t>
   </si>
   <si>
-    <t>BHPBLMIP1-Task4</t>
+    <t>learn</t>
   </si>
   <si>
-    <t>4. Teachers should implement the PBL Science lesson plan of class 8 "My Field My Crop" and upload photos or videos of the presentation</t>
+    <t>https://drive.google.com/file/d/1HOaFxlahxEzc5HOeFqVTw3V_yszmHFbZ/view?usp=drive_link</t>
   </si>
   <si>
-    <t>BHPBLMIP1-Task5</t>
+    <t>DPDTSC-HandBook-1-2025-Task5</t>
   </si>
   <si>
-    <t>5. Teachers should upload photos or videos of the presentation of Class 6 PBL Maths lesson plan Patterns Everywhere</t>
+    <t>Log into the scanner app and scan the OMR sheets (check that the students' names are appearing on scanning the OMR)</t>
+  </si>
+  <si>
+    <t>walking</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1eGLKxFb9BaeroTeIOlXoO8XCxyah7fM9/view?usp=sharing</t>
   </si>
   <si>
     <t>Please Provide the Name of the organization issuing the certificate.
@@ -571,26 +622,26 @@
     <t>Authorised Signatory - 2</t>
   </si>
   <si>
-    <t>Government of Tripura</t>
+    <t>Tan90</t>
   </si>
   <si>
     <t>One Logo - One Signature</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/14049mHsgj625Zcz8xOjcgk7c2iZi3VGI/view?usp=sharing</t>
+    <t>https://drive.google.com/file/d/1K-yUqtxu-Rw4F7cEW1Rz9nmo7INHeWcG/view?usp=drive_link</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1t6tD-TG5wU6CQAx98efK0nyOUbDU5gam/view?usp=drive_link</t>
+    <t>https://drive.google.com/file/d/16PLpbzvKxatX2YeUzqxcvQils-cC-J-j/view?usp=drive_link</t>
   </si>
   <si>
-    <t>Sajjan R.</t>
+    <t>Medha Krishnan R</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="20">
+  <fonts count="28">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -658,9 +709,36 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF1D1C1D"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="11.0"/>
       <color rgb="FF1D1C1D"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF1D1C1D"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Poppins"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -673,9 +751,21 @@
       <name val="Arial"/>
     </font>
     <font>
+      <u/>
       <sz val="11.0"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <color rgb="FF1155CC"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -754,7 +844,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="19">
     <border/>
     <border>
       <left style="thin">
@@ -872,11 +962,51 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="127">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1010,6 +1140,9 @@
     <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
+    <xf borderId="10" fillId="6" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    </xf>
     <xf borderId="0" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
@@ -1022,8 +1155,8 @@
     <xf borderId="0" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
@@ -1031,23 +1164,20 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="top"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf borderId="0" fillId="3" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="top"/>
+    <xf borderId="14" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="9" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1055,8 +1185,8 @@
     <xf borderId="0" fillId="9" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="9" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="0" fillId="9" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
@@ -1067,13 +1197,22 @@
     <xf borderId="0" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
+    <xf borderId="0" fillId="5" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="top"/>
+    </xf>
     <xf borderId="0" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="top"/>
+      <alignment readingOrder="0" vertical="top"/>
     </xf>
-    <xf borderId="10" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="11" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1082,62 +1221,11 @@
     <xf borderId="0" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf borderId="3" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="10" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    <xf borderId="15" fillId="8" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
@@ -1145,40 +1233,137 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="10" fillId="9" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="16" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="12" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="3" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="20" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="17" fillId="8" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf borderId="16" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="10" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="18" fillId="8" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="9" fontId="24" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="5" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="10" fillId="5" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="7" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="10" fillId="7" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="5" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="10" fillId="5" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="7" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="10" fillId="7" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="10" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="0" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="10" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="10" fillId="0" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf borderId="3" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -29796,16 +29981,19 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="28.75"/>
-    <col customWidth="1" min="2" max="3" width="19.13"/>
+    <col customWidth="1" min="2" max="2" width="19.13"/>
+    <col customWidth="1" min="3" max="3" width="29.38"/>
     <col customWidth="1" min="4" max="4" width="27.25"/>
     <col customWidth="1" min="5" max="5" width="17.38"/>
-    <col customWidth="1" min="6" max="8" width="19.75"/>
-    <col customWidth="1" min="9" max="9" width="29.88"/>
-    <col customWidth="1" min="10" max="10" width="46.63"/>
-    <col customWidth="1" min="11" max="11" width="20.25"/>
-    <col customWidth="1" min="12" max="14" width="19.13"/>
-    <col customWidth="1" min="15" max="15" width="37.88"/>
-    <col customWidth="1" min="17" max="17" width="21.13"/>
+    <col customWidth="1" min="6" max="9" width="19.75"/>
+    <col customWidth="1" min="10" max="10" width="29.88"/>
+    <col customWidth="1" min="11" max="11" width="46.63"/>
+    <col customWidth="1" min="12" max="12" width="21.63"/>
+    <col customWidth="1" min="13" max="13" width="23.88"/>
+    <col customWidth="1" min="14" max="14" width="22.25"/>
+    <col customWidth="1" min="15" max="15" width="19.13"/>
+    <col customWidth="1" min="16" max="16" width="37.88"/>
+    <col customWidth="1" min="18" max="18" width="21.13"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -29827,26 +30015,27 @@
       <c r="F1" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="G1" s="44" t="s">
+      <c r="G1" s="45"/>
+      <c r="H1" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="45" t="s">
+      <c r="I1" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="I1" s="45" t="s">
+      <c r="J1" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="J1" s="44" t="s">
+      <c r="K1" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="K1" s="46"/>
-      <c r="O1" s="47" t="s">
+      <c r="L1" s="46"/>
+      <c r="P1" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="P1" s="48" t="s">
+      <c r="Q1" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="Q1" s="48" t="s">
+      <c r="R1" s="48" t="s">
         <v>69</v>
       </c>
     </row>
@@ -29870,93 +30059,97 @@
         <v>48</v>
       </c>
       <c r="G2" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="H2" s="52" t="s">
+      <c r="I2" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="I2" s="52" t="s">
+      <c r="J2" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="52" t="s">
+      <c r="K2" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="K2" s="52" t="s">
+      <c r="L2" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="L2" s="52" t="s">
+      <c r="M2" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="M2" s="52" t="s">
-        <v>97</v>
-      </c>
-      <c r="N2" s="52" t="s">
+      <c r="N2" s="53" t="s">
         <v>98</v>
       </c>
       <c r="O2" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="P2" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="P2" s="54" t="s">
+      <c r="Q2" s="55" t="s">
         <v>65</v>
       </c>
-      <c r="Q2" s="54" t="s">
+      <c r="R2" s="55" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="3" ht="96.0" customHeight="1">
-      <c r="A3" s="55" t="s">
-        <v>99</v>
-      </c>
-      <c r="B3" s="56" t="s">
+      <c r="A3" s="56" t="s">
         <v>100</v>
       </c>
-      <c r="C3" s="57" t="s">
+      <c r="B3" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="D3" s="58" t="s">
+      <c r="C3" s="58" t="s">
         <v>102</v>
       </c>
-      <c r="E3" s="59" t="s">
+      <c r="D3" s="59" t="s">
         <v>103</v>
       </c>
-      <c r="F3" s="60" t="s">
+      <c r="E3" s="60" t="s">
         <v>104</v>
       </c>
-      <c r="G3" s="56"/>
-      <c r="H3" s="60" t="s">
+      <c r="F3" s="57" t="s">
         <v>105</v>
       </c>
-      <c r="I3" s="61"/>
-      <c r="J3" s="62" t="s">
+      <c r="G3" s="61" t="s">
         <v>106</v>
       </c>
-      <c r="K3" s="63"/>
-      <c r="L3" s="61"/>
-      <c r="M3" s="61"/>
-      <c r="N3" s="61"/>
-      <c r="O3" s="57" t="s">
+      <c r="H3" s="57"/>
+      <c r="I3" s="57" t="s">
         <v>107</v>
       </c>
-      <c r="P3" s="57" t="s">
-        <v>107</v>
+      <c r="J3" s="58"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="63"/>
+      <c r="M3" s="63"/>
+      <c r="N3" s="58"/>
+      <c r="O3" s="58"/>
+      <c r="P3" s="58" t="s">
+        <v>108</v>
       </c>
-      <c r="Q3" s="57">
-        <v>1.0</v>
+      <c r="Q3" s="58" t="s">
+        <v>108</v>
+      </c>
+      <c r="R3" s="58">
+        <v>2.0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="L1:O1"/>
   </mergeCells>
   <dataValidations>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D3">
-      <formula1>"teachers,students,infrastructure,community,educationLeader,schoolProcess"</formula1>
+      <formula1>"teachers,students,infrastructure,community,educationLeader,schoolProcess,Learner,faciliator"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G3">
+      <formula1>"school,block,district,cluster,state,Handbook1_Activity,Handbook2_Activity,Social Studies"</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink r:id="rId1" ref="J3"/>
-  </hyperlinks>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -29968,15 +30161,17 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="41.13"/>
-    <col customWidth="1" min="2" max="3" width="53.63"/>
-    <col customWidth="1" min="4" max="4" width="34.63"/>
-    <col customWidth="1" min="5" max="5" width="23.88"/>
-    <col customWidth="1" min="6" max="8" width="25.0"/>
-    <col customWidth="1" min="9" max="9" width="34.5"/>
-    <col customWidth="1" min="10" max="10" width="50.5"/>
-    <col customWidth="1" min="11" max="11" width="24.13"/>
-    <col customWidth="1" min="12" max="14" width="50.5"/>
-    <col customWidth="1" min="15" max="15" width="24.13"/>
+    <col customWidth="1" min="2" max="2" width="34.5"/>
+    <col customWidth="1" min="3" max="3" width="53.63"/>
+    <col customWidth="1" min="4" max="6" width="34.63"/>
+    <col customWidth="1" min="7" max="7" width="23.88"/>
+    <col customWidth="1" min="8" max="8" width="32.38"/>
+    <col customWidth="1" min="9" max="9" width="30.38"/>
+    <col customWidth="1" min="10" max="10" width="34.5"/>
+    <col customWidth="1" min="11" max="15" width="50.5"/>
+    <col customWidth="1" min="16" max="17" width="37.38"/>
+    <col customWidth="1" min="18" max="20" width="50.5"/>
+    <col customWidth="1" min="21" max="23" width="24.13"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -29984,46 +30179,70 @@
         <v>14</v>
       </c>
       <c r="B1" s="64" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C1" s="65" t="s">
         <v>22</v>
       </c>
       <c r="D1" s="64" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E1" s="64" t="s">
+        <v>111</v>
+      </c>
+      <c r="F1" s="64" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="64" t="s">
+      <c r="H1" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="66" t="s">
-        <v>110</v>
-      </c>
-      <c r="H1" s="64" t="s">
+      <c r="I1" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="64" t="s">
+      <c r="J1" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="J1" s="64" t="s">
-        <v>111</v>
-      </c>
-      <c r="K1" s="65" t="s">
-        <v>112</v>
+      <c r="K1" s="64" t="s">
+        <v>31</v>
       </c>
       <c r="L1" s="64" t="s">
+        <v>35</v>
+      </c>
+      <c r="M1" s="64" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" s="64" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="M1" s="65" t="s">
+      <c r="P1" s="65" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q1" s="66" t="s">
+        <v>115</v>
+      </c>
+      <c r="R1" s="64" t="s">
+        <v>116</v>
+      </c>
+      <c r="S1" s="65" t="s">
         <v>51</v>
       </c>
-      <c r="N1" s="65" t="s">
-        <v>114</v>
+      <c r="T1" s="65" t="s">
+        <v>117</v>
       </c>
-      <c r="O1" s="65" t="s">
-        <v>115</v>
+      <c r="U1" s="65" t="s">
+        <v>118</v>
+      </c>
+      <c r="V1" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="W1" s="64" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
@@ -30040,177 +30259,283 @@
         <v>19</v>
       </c>
       <c r="E2" s="70" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
-      <c r="F2" s="69" t="s">
+      <c r="F2" s="71" t="s">
+        <v>112</v>
+      </c>
+      <c r="G2" s="72" t="s">
+        <v>119</v>
+      </c>
+      <c r="H2" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="71" t="s">
-        <v>116</v>
-      </c>
-      <c r="H2" s="72" t="s">
+      <c r="I2" s="73" t="s">
         <v>30</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="J2" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="70" t="s">
+      <c r="K2" s="74" t="s">
         <v>38</v>
       </c>
-      <c r="K2" s="72" t="s">
+      <c r="L2" s="74" t="s">
         <v>42</v>
       </c>
-      <c r="L2" s="73" t="s">
+      <c r="M2" s="74" t="s">
+        <v>98</v>
+      </c>
+      <c r="N2" s="74" t="s">
+        <v>99</v>
+      </c>
+      <c r="O2" s="72" t="s">
+        <v>120</v>
+      </c>
+      <c r="P2" s="74" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q2" s="75" t="s">
+        <v>122</v>
+      </c>
+      <c r="R2" s="76" t="s">
         <v>46</v>
       </c>
-      <c r="M2" s="73" t="s">
+      <c r="S2" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="N2" s="74" t="s">
-        <v>117</v>
+      <c r="T2" s="77" t="s">
+        <v>123</v>
       </c>
-      <c r="O2" s="75" t="s">
-        <v>118</v>
+      <c r="U2" s="77" t="s">
+        <v>124</v>
       </c>
+      <c r="V2" s="78" t="s">
+        <v>71</v>
+      </c>
+      <c r="W2" s="78" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="59" t="s">
-        <v>119</v>
+      <c r="A3" s="60" t="s">
+        <v>125</v>
       </c>
-      <c r="B3" s="59" t="s">
-        <v>120</v>
+      <c r="B3" s="79" t="s">
+        <v>126</v>
       </c>
-      <c r="C3" s="59" t="s">
-        <v>107</v>
+      <c r="C3" s="80" t="s">
+        <v>127</v>
       </c>
-      <c r="D3" s="61"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="61"/>
-      <c r="K3" s="61"/>
-      <c r="L3" s="80" t="s">
-        <v>121</v>
+      <c r="D3" s="81"/>
+      <c r="E3" s="82" t="s">
+        <v>127</v>
       </c>
-      <c r="M3" s="81">
+      <c r="F3" s="83" t="s">
+        <v>128</v>
+      </c>
+      <c r="G3" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="H3" s="58">
+        <v>1.0</v>
+      </c>
+      <c r="I3" s="84"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="86"/>
+      <c r="L3" s="87"/>
+      <c r="M3" s="86"/>
+      <c r="N3" s="87"/>
+      <c r="O3" s="86"/>
+      <c r="P3" s="87"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="89" t="s">
+        <v>127</v>
+      </c>
+      <c r="S3" s="90">
         <v>2.0</v>
       </c>
-      <c r="N3" s="82" t="s">
-        <v>121</v>
-      </c>
-      <c r="O3" s="57"/>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="59" t="s">
-        <v>122</v>
-      </c>
-      <c r="B4" s="83" t="s">
-        <v>123</v>
-      </c>
-      <c r="C4" s="59" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" s="84"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="85"/>
-      <c r="I4" s="78"/>
-      <c r="J4" s="61"/>
-      <c r="K4" s="61"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
-      <c r="N4" s="86" t="s">
-        <v>107</v>
-      </c>
-      <c r="O4" s="57"/>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="83" t="s">
-        <v>124</v>
-      </c>
-      <c r="B5" s="83" t="s">
-        <v>125</v>
-      </c>
-      <c r="C5" s="83" t="s">
-        <v>107</v>
-      </c>
-      <c r="D5" s="87"/>
-      <c r="E5" s="88"/>
-      <c r="F5" s="87"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="90"/>
-      <c r="J5" s="91"/>
-      <c r="K5" s="61"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="21"/>
-      <c r="N5" s="86" t="s">
-        <v>121</v>
-      </c>
-      <c r="O5" s="91"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="83" t="s">
-        <v>126</v>
-      </c>
-      <c r="B6" s="83" t="s">
+      <c r="T3" s="91" t="s">
         <v>127</v>
       </c>
-      <c r="C6" s="83" t="s">
-        <v>107</v>
+      <c r="U3" s="92">
+        <v>2.0</v>
       </c>
-      <c r="D6" s="87"/>
-      <c r="E6" s="92"/>
-      <c r="F6" s="87"/>
-      <c r="G6" s="77"/>
-      <c r="H6" s="89"/>
-      <c r="I6" s="90"/>
-      <c r="J6" s="91"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="21"/>
-      <c r="N6" s="86" t="s">
-        <v>107</v>
+      <c r="V3" s="93" t="s">
+        <v>130</v>
       </c>
-      <c r="O6" s="93">
-        <v>1.0</v>
+      <c r="W3" s="94" t="s">
+        <v>131</v>
       </c>
     </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="60" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4" s="95" t="s">
+        <v>133</v>
+      </c>
+      <c r="C4" s="80" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4" s="96"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="84" t="s">
+        <v>134</v>
+      </c>
+      <c r="J4" s="85" t="s">
+        <v>135</v>
+      </c>
+      <c r="K4" s="86"/>
+      <c r="L4" s="86"/>
+      <c r="M4" s="86"/>
+      <c r="N4" s="86"/>
+      <c r="O4" s="86"/>
+      <c r="P4" s="87"/>
+      <c r="Q4" s="87"/>
+      <c r="R4" s="98"/>
+      <c r="S4" s="21"/>
+      <c r="T4" s="99" t="s">
+        <v>136</v>
+      </c>
+      <c r="U4" s="100"/>
+      <c r="V4" s="93" t="s">
+        <v>130</v>
+      </c>
+      <c r="W4" s="94" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="60" t="s">
+        <v>137</v>
+      </c>
+      <c r="B5" s="95" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" s="80" t="s">
+        <v>127</v>
+      </c>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="101"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="86"/>
+      <c r="J5" s="102"/>
+      <c r="K5" s="86"/>
+      <c r="L5" s="103"/>
+      <c r="M5" s="86"/>
+      <c r="N5" s="103"/>
+      <c r="O5" s="86"/>
+      <c r="P5" s="87"/>
+      <c r="Q5" s="87"/>
+      <c r="R5" s="98"/>
+      <c r="S5" s="21"/>
+      <c r="T5" s="99" t="s">
+        <v>127</v>
+      </c>
+      <c r="U5" s="104">
+        <v>2.0</v>
+      </c>
+      <c r="V5" s="93" t="s">
+        <v>130</v>
+      </c>
+      <c r="W5" s="94" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="60" t="s">
+        <v>139</v>
+      </c>
+      <c r="B6" s="95" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" s="80" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="105"/>
+      <c r="H6" s="82"/>
+      <c r="I6" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="J6" s="106" t="s">
+        <v>142</v>
+      </c>
+      <c r="K6" s="84"/>
+      <c r="L6" s="107"/>
+      <c r="M6" s="86"/>
+      <c r="N6" s="103"/>
+      <c r="O6" s="86"/>
+      <c r="P6" s="87"/>
+      <c r="Q6" s="87"/>
+      <c r="R6" s="98"/>
+      <c r="S6" s="21"/>
+      <c r="T6" s="99" t="s">
+        <v>136</v>
+      </c>
+      <c r="U6" s="108"/>
+      <c r="V6" s="93" t="s">
+        <v>130</v>
+      </c>
+      <c r="W6" s="94" t="s">
+        <v>131</v>
+      </c>
+    </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="94" t="s">
-        <v>128</v>
+      <c r="A7" s="60" t="s">
+        <v>143</v>
       </c>
-      <c r="B7" s="94" t="s">
-        <v>129</v>
+      <c r="B7" s="109" t="s">
+        <v>144</v>
       </c>
-      <c r="C7" s="83" t="s">
-        <v>107</v>
+      <c r="C7" s="80" t="s">
+        <v>127</v>
       </c>
-      <c r="D7" s="95"/>
-      <c r="E7" s="95"/>
-      <c r="F7" s="87"/>
-      <c r="G7" s="77"/>
-      <c r="H7" s="89"/>
-      <c r="I7" s="90"/>
-      <c r="J7" s="95"/>
-      <c r="K7" s="95"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="38"/>
-      <c r="N7" s="86" t="s">
-        <v>121</v>
+      <c r="D7" s="110"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="110"/>
+      <c r="G7" s="110"/>
+      <c r="H7" s="82"/>
+      <c r="I7" s="111" t="s">
+        <v>145</v>
       </c>
-      <c r="O7" s="95"/>
+      <c r="J7" s="112" t="s">
+        <v>146</v>
+      </c>
+      <c r="K7" s="86"/>
+      <c r="L7" s="113"/>
+      <c r="M7" s="86"/>
+      <c r="N7" s="113"/>
+      <c r="O7" s="86"/>
+      <c r="P7" s="113"/>
+      <c r="Q7" s="113"/>
+      <c r="R7" s="98"/>
+      <c r="S7" s="38"/>
+      <c r="T7" s="99" t="s">
+        <v>136</v>
+      </c>
+      <c r="U7" s="114"/>
+      <c r="V7" s="93" t="s">
+        <v>130</v>
+      </c>
+      <c r="W7" s="94" t="s">
+        <v>131</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="L3:L7"/>
-    <mergeCell ref="M3:M7"/>
+    <mergeCell ref="R3:R7"/>
+    <mergeCell ref="S3:S7"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R3">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D3:D6">
@@ -30219,11 +30544,22 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C3:C7">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N3:N7">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E3:E7">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F3:F7">
+      <formula1>"observation,survey,improvementProject,Googlesheet"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="T3:T7">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
-  <drawing r:id="rId1"/>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="J4"/>
+    <hyperlink r:id="rId2" ref="J6"/>
+    <hyperlink r:id="rId3" ref="J7"/>
+  </hyperlinks>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -30245,76 +30581,76 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="96" t="s">
-        <v>130</v>
+      <c r="A1" s="115" t="s">
+        <v>147</v>
       </c>
-      <c r="B1" s="96" t="s">
-        <v>131</v>
+      <c r="B1" s="115" t="s">
+        <v>148</v>
       </c>
-      <c r="C1" s="96" t="s">
-        <v>132</v>
+      <c r="C1" s="115" t="s">
+        <v>149</v>
       </c>
-      <c r="D1" s="96" t="s">
+      <c r="D1" s="115" t="s">
         <v>81</v>
       </c>
-      <c r="E1" s="96" t="s">
-        <v>133</v>
+      <c r="E1" s="115" t="s">
+        <v>150</v>
       </c>
-      <c r="F1" s="96" t="s">
-        <v>134</v>
+      <c r="F1" s="115" t="s">
+        <v>151</v>
       </c>
-      <c r="G1" s="96" t="s">
-        <v>135</v>
+      <c r="G1" s="115" t="s">
+        <v>152</v>
       </c>
-      <c r="H1" s="96" t="s">
-        <v>136</v>
+      <c r="H1" s="115" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="97" t="s">
+      <c r="A2" s="116" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="97" t="s">
+      <c r="B2" s="116" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="97" t="s">
+      <c r="C2" s="116" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="98" t="s">
+      <c r="D2" s="117" t="s">
         <v>80</v>
       </c>
-      <c r="E2" s="97" t="s">
+      <c r="E2" s="116" t="s">
         <v>83</v>
       </c>
-      <c r="F2" s="99" t="s">
+      <c r="F2" s="118" t="s">
         <v>85</v>
       </c>
-      <c r="G2" s="98" t="s">
+      <c r="G2" s="117" t="s">
         <v>88</v>
       </c>
-      <c r="H2" s="100" t="s">
-        <v>137</v>
+      <c r="H2" s="119" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="101" t="s">
-        <v>138</v>
+      <c r="A3" s="120" t="s">
+        <v>155</v>
       </c>
-      <c r="B3" s="102" t="s">
-        <v>139</v>
+      <c r="B3" s="121" t="s">
+        <v>156</v>
       </c>
-      <c r="C3" s="103" t="s">
-        <v>140</v>
+      <c r="C3" s="122" t="s">
+        <v>157</v>
       </c>
-      <c r="D3" s="104"/>
-      <c r="E3" s="105" t="s">
-        <v>141</v>
+      <c r="D3" s="123"/>
+      <c r="E3" s="124" t="s">
+        <v>158</v>
       </c>
-      <c r="F3" s="106" t="s">
-        <v>142</v>
+      <c r="F3" s="125" t="s">
+        <v>159</v>
       </c>
-      <c r="G3" s="107"/>
-      <c r="H3" s="107"/>
+      <c r="G3" s="126"/>
+      <c r="H3" s="126"/>
     </row>
   </sheetData>
   <dataValidations>
